--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -468,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -587,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>2343</v>
+        <v>2068</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2889</v>
+        <v>2369</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-546</v>
+        <v>-301</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -636,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2348</v>
+        <v>1858</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2889</v>
+        <v>2044</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-541</v>
+        <v>-186</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1858</v>
+        <v>1298</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2044</v>
+        <v>1126</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-186</v>
+        <v>172</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1298</v>
+        <v>1018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1126</v>
+        <v>856</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1018</v>
+        <v>1088</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>162</v>
+        <v>232</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>943</v>
+        <v>1088</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -861,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1088</v>
+        <v>1018</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -909,10 +918,10 @@
         <v>943</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>926</v>
+        <v>1038</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>17</v>
+        <v>-95</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>40</v>
@@ -923,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +960,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1088</v>
+        <v>1158</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>926</v>
+        <v>1038</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>162</v>
+        <v>120</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46</v>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1018</v>
+        <v>1298</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1044,10 +1053,10 @@
         <v>1158</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>926</v>
+        <v>1038</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>232</v>
+        <v>120</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1086,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1298</v>
+        <v>2348</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1126</v>
+        <v>2306</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1158</v>
+        <v>2348</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1038</v>
+        <v>2306</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1158</v>
+        <v>2348</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1038</v>
+        <v>2306</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1387,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2348</v>
+        <v>643</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2306</v>
+        <v>505</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1424,231 +1433,6 @@
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>20-JUL-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-8246</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>2348</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>2306</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-8246</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>2348</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>2306</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>03-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-279</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-279</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-279</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>505</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -48,6 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
@@ -56,12 +62,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>flyadeal F3-613</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1333</v>
+        <v>1169</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1784</v>
+        <v>2044</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-451</v>
+        <v>-875</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-352</t>
+          <t>Nile Air NP-154</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1529</v>
+        <v>1333</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1784</v>
+        <v>2044</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-255</v>
+        <v>-711</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -617,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1535</v>
+        <v>1335</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1784</v>
+        <v>2044</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-249</v>
+        <v>-709</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,28 +686,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1573</v>
+        <v>2068</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1784</v>
+        <v>2044</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-211</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1613</v>
+        <v>963</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1784</v>
+        <v>926</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-171</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-354</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1333</v>
+        <v>1088</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2044</v>
+        <v>926</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-711</v>
+        <v>162</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-154</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1333</v>
+        <v>529</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2044</v>
+        <v>856</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-711</v>
+        <v>-327</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1333</v>
+        <v>529</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2044</v>
+        <v>856</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-711</v>
+        <v>-327</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1858</v>
+        <v>628</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2044</v>
+        <v>856</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-186</v>
+        <v>-228</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>963</v>
+        <v>1018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>926</v>
+        <v>856</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1088</v>
+        <v>479</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>162</v>
+        <v>-447</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>624</v>
+        <v>479</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-232</v>
+        <v>-447</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>624</v>
+        <v>500</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-232</v>
+        <v>-426</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>624</v>
+        <v>1088</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-232</v>
+        <v>162</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,417 +1157,12 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>01-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-8246</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>856</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-652</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>594</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-332</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-650</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>604</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-322</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-690</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>604</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-322</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-279</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>853</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-73</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-8246</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1088</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>162</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-650</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>571</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>724</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-153</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15-JUN-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-152</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>599</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>856</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-257</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-8246</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>1088</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>856</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>232</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -465,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-613</t>
+          <t>Air Arabia Egypt E5-416</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1169</v>
+        <v>1035</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-875</v>
+        <v>-1009</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-154</t>
+          <t>flyadeal F3-613</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1333</v>
+        <v>1169</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-711</v>
+        <v>-875</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>Nesma Airlines NE-165</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>963</v>
+        <v>1088</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>28-MAY-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1088</v>
+        <v>604</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>926</v>
+        <v>856</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>162</v>
+        <v>-252</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>529</v>
+        <v>604</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-327</v>
+        <v>-252</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>529</v>
+        <v>628</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-327</v>
+        <v>-228</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>628</v>
+        <v>1018</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-228</v>
+        <v>162</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1018</v>
+        <v>479</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>162</v>
+        <v>-447</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-447</v>
+        <v>-426</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>500</v>
+        <v>1088</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-426</v>
+        <v>162</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,33 +1136,2193 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>Nesma Airlines NE-163</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-224</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-224</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-195</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-285</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-270</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-262</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>15-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-8246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>1088</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>926</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="D21" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-291</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>18-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>22-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>25-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1298</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>29-JUN-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1038</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-411</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-886</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-273</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-867</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-771</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>02-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-152</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-1132</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-252</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-1132</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-161</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-1131</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-152</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-1263</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-1085</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-1070</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-1712</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-1660</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-1527</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-323</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-1843</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-311</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-1843</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-321</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>613</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-1693</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-411</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-1833</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-1785</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-1777</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-1735</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>661</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-1645</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>669</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-1637</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-8246</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-87</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-323</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-113</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>03-SEP-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-416</t>
+          <t>Nile Air NP-354</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1035</v>
+        <v>1333</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1009</v>
+        <v>-711</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-613</t>
+          <t>Nile Air NP-154</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1169</v>
+        <v>1333</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-875</v>
+        <v>-711</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-165</t>
+          <t>Nile Air NP-352</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-709</v>
+        <v>-711</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2068</v>
+        <v>1858</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>24</v>
+        <v>-186</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1088</v>
+        <v>963</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>604</v>
+        <v>1088</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-252</v>
+        <v>162</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-228</v>
+        <v>-252</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,7 +887,7 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1018</v>
+        <v>628</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>162</v>
+        <v>-228</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>01-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>479</v>
+        <v>1018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>926</v>
+        <v>856</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-447</v>
+        <v>162</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-447</v>
+        <v>-426</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-287</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>500</v>
+        <v>703</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-426</v>
+        <v>-223</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1091,28 +1091,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-265</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1088</v>
+        <v>703</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>162</v>
+        <v>-223</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>500</v>
+        <v>853</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>724</v>
+        <v>926</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-224</v>
+        <v>-73</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>500</v>
+        <v>1088</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>724</v>
+        <v>926</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-224</v>
+        <v>162</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-195</v>
+        <v>-224</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>571</v>
+        <v>529</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-285</v>
+        <v>-195</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>586</v>
+        <v>500</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-270</v>
+        <v>-224</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>594</v>
+        <v>500</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-262</v>
+        <v>-224</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1018</v>
+        <v>604</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>162</v>
+        <v>-120</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>835</v>
+        <v>853</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1126</v>
+        <v>724</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-291</v>
+        <v>129</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1298</v>
+        <v>571</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1126</v>
+        <v>856</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>172</v>
+        <v>-285</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1298</v>
+        <v>586</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1126</v>
+        <v>856</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>172</v>
+        <v>-270</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1298</v>
+        <v>594</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1126</v>
+        <v>856</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>172</v>
+        <v>-262</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1158</v>
+        <v>1018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1038</v>
+        <v>856</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46</v>
@@ -1652,7 +1652,7 @@
       <c r="I26" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1420</v>
+        <v>835</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2306</v>
+        <v>1126</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-886</v>
+        <v>-291</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1439</v>
+        <v>1298</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2306</v>
+        <v>1126</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-867</v>
+        <v>172</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1535</v>
+        <v>1298</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2306</v>
+        <v>1126</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-771</v>
+        <v>172</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2348</v>
+        <v>1298</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>2306</v>
+        <v>1126</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1832,7 +1832,7 @@
       <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1174</v>
+        <v>1158</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2306</v>
+        <v>1038</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-1132</v>
+        <v>120</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-252</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1174</v>
+        <v>1420</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-1132</v>
+        <v>-886</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1175</v>
+        <v>1439</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-1131</v>
+        <v>-867</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2348</v>
+        <v>1535</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>42</v>
+        <v>-771</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1043</v>
+        <v>2348</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1263</v>
+        <v>42</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1221</v>
+        <v>1174</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1085</v>
+        <v>-1132</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1236</v>
+        <v>1174</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1070</v>
+        <v>-1132</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2348</v>
+        <v>1244</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>42</v>
+        <v>-1062</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2192,9 +2192,9 @@
       <c r="I38" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>594</v>
+        <v>2348</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1712</v>
+        <v>42</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>46</v>
@@ -2237,9 +2237,9 @@
       <c r="I39" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>646</v>
+        <v>1045</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1660</v>
+        <v>-1261</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>779</v>
+        <v>1221</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1527</v>
+        <v>-1085</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2348</v>
+        <v>1236</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>42</v>
+        <v>-1070</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>463</v>
+        <v>2348</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1843</v>
+        <v>42</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>463</v>
+        <v>545</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1843</v>
+        <v>-1761</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,26 +2486,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1693</v>
+        <v>-1761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-313</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2348</v>
+        <v>545</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>42</v>
+        <v>-1761</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,9 +2552,9 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>473</v>
+        <v>2348</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1833</v>
+        <v>42</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>521</v>
+        <v>463</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1785</v>
+        <v>-1843</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>23</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Saudia SV-311</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>529</v>
+        <v>463</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1777</v>
+        <v>-1843</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2348</v>
+        <v>613</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>42</v>
+        <v>-1693</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>571</v>
+        <v>2348</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1735</v>
+        <v>42</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>46</v>
@@ -2777,9 +2777,9 @@
       <c r="I51" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>661</v>
+        <v>521</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-1645</v>
+        <v>-1785</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>669</v>
+        <v>529</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1637</v>
+        <v>-1777</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-313</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2348</v>
+        <v>624</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>42</v>
+        <v>-1682</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>571</v>
+        <v>2348</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>658</v>
+        <v>2306</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-87</v>
+        <v>42</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2957,7 +2957,7 @@
       <c r="I55" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>658</v>
+        <v>2306</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-113</v>
+        <v>-1735</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3030,13 +3030,13 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>586</v>
+        <v>661</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>658</v>
+        <v>2306</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-72</v>
+        <v>-1645</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3047,9 +3047,9 @@
       <c r="I57" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>594</v>
+        <v>669</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>658</v>
+        <v>2306</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-64</v>
+        <v>-1637</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,9 +3092,9 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>529</v>
+        <v>2348</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>505</v>
+        <v>2306</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3137,7 +3137,7 @@
       <c r="I59" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       <c r="I60" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>529</v>
+        <v>646</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>24</v>
+        <v>-12</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3227,7 +3227,7 @@
       <c r="I61" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>24</v>
+        <v>-113</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,7 +3272,7 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3286,43 +3286,403 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-54</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>10-SEP-26</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-690</t>
         </is>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D69" s="2" t="n">
         <v>529</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>505</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="F69" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="G63" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="G69" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-279</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>17-SEP-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-354</t>
+          <t>Nile Air NP-352</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-352</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>853</v>
+        <v>1088</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-73</v>
+        <v>162</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1088</v>
+        <v>500</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>926</v>
+        <v>724</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>162</v>
+        <v>-224</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-224</v>
+        <v>-195</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-195</v>
+        <v>-224</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>500</v>
+        <v>604</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-224</v>
+        <v>-120</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>604</v>
+        <v>853</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-120</v>
+        <v>129</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>853</v>
+        <v>571</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>724</v>
+        <v>856</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>129</v>
+        <v>-285</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-285</v>
+        <v>-270</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-270</v>
+        <v>-262</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1586,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>594</v>
+        <v>1018</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-262</v>
+        <v>162</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1607,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>15-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1018</v>
+        <v>835</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>162</v>
+        <v>-291</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -1676,26 +1676,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>835</v>
+        <v>1298</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1126</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-291</v>
+        <v>172</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1815,13 +1815,13 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1298</v>
+        <v>1158</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1126</v>
+        <v>1038</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1158</v>
+        <v>1420</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1038</v>
+        <v>2306</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>120</v>
+        <v>-886</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1901,26 +1901,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1420</v>
+        <v>1535</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-886</v>
+        <v>-771</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-273</t>
+          <t>flyadeal F3-605</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1439</v>
+        <v>1646</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-867</v>
+        <v>-660</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1535</v>
+        <v>2348</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-771</v>
+        <v>42</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2348</v>
+        <v>1174</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>42</v>
+        <v>-1132</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2081,26 +2081,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1174</v>
+        <v>1244</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1132</v>
+        <v>-1062</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-252</t>
+          <t>flynas XY-269</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1174</v>
+        <v>1313</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-1132</v>
+        <v>-993</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1244</v>
+        <v>2348</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-1062</v>
+        <v>42</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>46</v>
@@ -2192,9 +2192,9 @@
       <c r="I38" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>2348</v>
+        <v>1045</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>42</v>
+        <v>-1261</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1045</v>
+        <v>1221</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1261</v>
+        <v>-1085</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1221</v>
+        <v>1236</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1085</v>
+        <v>-1070</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1236</v>
+        <v>2348</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-1070</v>
+        <v>42</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2348</v>
+        <v>545</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>42</v>
+        <v>-1761</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2417,9 +2417,9 @@
       <c r="I43" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>545</v>
+        <v>646</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-1761</v>
+        <v>-1660</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>46</v>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>545</v>
+        <v>2348</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-1761</v>
+        <v>42</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,9 +2552,9 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2348</v>
+        <v>463</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>42</v>
+        <v>-1843</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2621,26 +2621,26 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>Saudia SV-311</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>463</v>
+        <v>545</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1843</v>
+        <v>-1761</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>463</v>
+        <v>695</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1843</v>
+        <v>-1611</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>613</v>
+        <v>2348</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-1693</v>
+        <v>42</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2348</v>
+        <v>473</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>42</v>
+        <v>-1833</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-1785</v>
+        <v>-1777</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Saudia SV-313</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>529</v>
+        <v>624</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1777</v>
+        <v>-1682</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>624</v>
+        <v>2348</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-1682</v>
+        <v>42</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>2348</v>
+        <v>571</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>42</v>
+        <v>-1735</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2957,9 +2957,9 @@
       <c r="I55" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>571</v>
+        <v>661</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1735</v>
+        <v>-1645</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1645</v>
+        <v>-1637</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>669</v>
+        <v>2348</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-1637</v>
+        <v>42</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,9 +3092,9 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>2348</v>
+        <v>529</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2306</v>
+        <v>505</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>529</v>
+        <v>646</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>24</v>
+        <v>-12</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Saudia SV-311</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>646</v>
+        <v>545</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>658</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-12</v>
+        <v>-113</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>658</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-113</v>
+        <v>-72</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>658</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-72</v>
+        <v>-64</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>594</v>
+        <v>529</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-64</v>
+        <v>24</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>46</v>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>604</v>
+        <v>529</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-54</v>
+        <v>24</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>529</v>
+        <v>643</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>505</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>17-SEP-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,26 +3611,26 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>643</v>
+        <v>529</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>505</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
@@ -3656,26 +3656,26 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>529</v>
+        <v>643</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>505</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -551,26 +551,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-352</t>
+          <t>Air Arabia Egypt E5-416</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1333</v>
+        <v>1248</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>2044</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-711</v>
+        <v>-796</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>500</v>
+        <v>479</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-426</v>
+        <v>-447</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-287</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>703</v>
+        <v>479</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-223</v>
+        <v>-447</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-265</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>703</v>
+        <v>500</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-223</v>
+        <v>-426</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1088</v>
+        <v>853</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>926</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>162</v>
+        <v>-73</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>500</v>
+        <v>1088</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>724</v>
+        <v>926</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-224</v>
+        <v>162</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>529</v>
+        <v>500</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-195</v>
+        <v>-224</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-163</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-224</v>
+        <v>-195</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1361,26 +1361,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>604</v>
+        <v>500</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-120</v>
+        <v>-224</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>853</v>
+        <v>604</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>724</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>129</v>
+        <v>-120</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-270</v>
+        <v>-262</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>856</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-262</v>
+        <v>-252</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1298</v>
+        <v>1023</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1126</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>172</v>
+        <v>-103</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,26 +1811,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1158</v>
+        <v>1273</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1038</v>
+        <v>1126</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1420</v>
+        <v>1298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2306</v>
+        <v>1126</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-886</v>
+        <v>172</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1535</v>
+        <v>1158</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2306</v>
+        <v>1038</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-771</v>
+        <v>120</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-605</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1646</v>
+        <v>1420</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-660</v>
+        <v>-886</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>flynas XY-273</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>2348</v>
+        <v>1439</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>42</v>
+        <v>-867</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-152</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1174</v>
+        <v>1535</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-1132</v>
+        <v>-771</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>30</v>
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1244</v>
+        <v>2348</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-1062</v>
+        <v>42</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>46</v>
@@ -2102,9 +2102,9 @@
       <c r="I36" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,26 +2126,26 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>1313</v>
+        <v>1174</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-993</v>
+        <v>-1132</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2348</v>
+        <v>1174</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>42</v>
+        <v>-1132</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,26 +2216,26 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1045</v>
+        <v>1244</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-1261</v>
+        <v>-1062</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1221</v>
+        <v>2348</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-1085</v>
+        <v>42</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>46</v>
@@ -2282,9 +2282,9 @@
       <c r="I40" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1236</v>
+        <v>1045</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-1070</v>
+        <v>-1261</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2348</v>
+        <v>1221</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>42</v>
+        <v>-1085</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>46</v>
@@ -2372,9 +2372,9 @@
       <c r="I42" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>545</v>
+        <v>1236</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-1761</v>
+        <v>-1070</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>46</v>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>545</v>
+        <v>2348</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-1761</v>
+        <v>42</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>46</v>
@@ -2462,9 +2462,9 @@
       <c r="I44" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2348</v>
+        <v>669</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>42</v>
+        <v>-1637</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>46</v>
@@ -2552,9 +2552,9 @@
       <c r="I46" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,26 +2576,26 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>463</v>
+        <v>779</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-1843</v>
+        <v>-1527</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>545</v>
+        <v>2348</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-1761</v>
+        <v>42</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>46</v>
@@ -2642,9 +2642,9 @@
       <c r="I48" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-321</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>695</v>
+        <v>463</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-1611</v>
+        <v>-1843</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-311</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2348</v>
+        <v>463</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>42</v>
+        <v>-1843</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>473</v>
+        <v>695</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-1833</v>
+        <v>-1611</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>529</v>
+        <v>2348</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-1777</v>
+        <v>42</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>46</v>
@@ -2822,9 +2822,9 @@
       <c r="I52" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>Air Arabia Egypt E5-411</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>624</v>
+        <v>473</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-1682</v>
+        <v>-1833</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2348</v>
+        <v>529</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>42</v>
+        <v>-1777</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>46</v>
@@ -2912,9 +2912,9 @@
       <c r="I54" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>571</v>
+        <v>624</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-1735</v>
+        <v>-1682</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>46</v>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>661</v>
+        <v>2348</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-1645</v>
+        <v>42</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>669</v>
+        <v>571</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-1637</v>
+        <v>-1735</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3071,17 +3071,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2348</v>
+        <v>661</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>2306</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>42</v>
+        <v>-1645</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>46</v>
@@ -3092,9 +3092,9 @@
       <c r="I58" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>529</v>
+        <v>669</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>505</v>
+        <v>2306</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>24</v>
+        <v>-1637</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>46</v>
@@ -3137,9 +3137,9 @@
       <c r="I59" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,17 +3161,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>646</v>
+        <v>2348</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>658</v>
+        <v>2306</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-12</v>
+        <v>42</v>
       </c>
       <c r="G60" s="2" t="n">
         <v>46</v>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>658</v>
+        <v>505</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-113</v>
+        <v>24</v>
       </c>
       <c r="G61" s="2" t="n">
         <v>46</v>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>Saudia SV-323</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>658</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-72</v>
+        <v>-34</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>594</v>
+        <v>646</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>658</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-64</v>
+        <v>-12</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>46</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>529</v>
+        <v>586</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>46</v>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>529</v>
+        <v>594</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>24</v>
+        <v>-64</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>46</v>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>27-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3435,13 +3435,13 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>529</v>
+        <v>604</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>24</v>
+        <v>-54</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>03-SEP-26</t>
+          <t>20-AUG-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>643</v>
+        <v>529</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>505</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>138</v>
+        <v>24</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>10-SEP-26</t>
+          <t>27-AUG-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17-SEP-26</t>
+          <t>03-SEP-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">

--- a/excel_routes/route_RUH_HMB_threats.xlsx
+++ b/excel_routes/route_RUH_HMB_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -532,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,30 +551,30 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-354</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>790</v>
+        <v>1038</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-391</v>
+        <v>-688</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +596,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-352</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>399</v>
+        <v>350</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>790</v>
+        <v>1038</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-391</v>
+        <v>-688</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-313</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>545</v>
+        <v>399</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>790</v>
+        <v>1038</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-245</v>
+        <v>-639</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-161</t>
+          <t>flynas XY-279</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>401</v>
+        <v>793</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>790</v>
+        <v>1038</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-389</v>
+        <v>-245</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>608</v>
+        <v>350</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>790</v>
+        <v>658</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-182</v>
+        <v>-308</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>Nile Air NP-352</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>623</v>
+        <v>350</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>790</v>
+        <v>658</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-167</v>
+        <v>-308</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,28 +821,28 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>Nile Air NP-252</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>631</v>
+        <v>350</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>790</v>
+        <v>658</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-159</v>
+        <v>-308</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,28 +866,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-279</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1123</v>
+        <v>401</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1038</v>
+        <v>724</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>85</v>
+        <v>-323</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>15-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,28 +911,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-163</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1196</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1038</v>
+        <v>724</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>158</v>
+        <v>-224</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,28 +956,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nesma Airlines NE-161</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1336</v>
+        <v>745</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1126</v>
+        <v>1038</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>210</v>
+        <v>-293</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,28 +1001,28 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Nile Air NP-152</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1336</v>
+        <v>834</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1126</v>
+        <v>1038</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>210</v>
+        <v>-204</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1196</v>
+        <v>931</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1038</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>158</v>
+        <v>-107</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1058,7 +1067,7 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1072,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1103,7 +1112,7 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1117,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1196</v>
+        <v>1111</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1038</v>
+        <v>1126</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>158</v>
+        <v>-15</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1148,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1196</v>
+        <v>1126</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1038</v>
+        <v>1126</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1193,7 +1202,7 @@
       <c r="I16" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1207,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>683</v>
+        <v>1134</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-173</v>
+        <v>8</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1238,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>706</v>
+        <v>1336</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-150</v>
+        <v>210</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1283,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>816</v>
+        <v>1156</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-40</v>
+        <v>30</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1328,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1342,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1356,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1056</v>
+        <v>1336</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>856</v>
+        <v>1126</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1373,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1387,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-323</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>542</v>
+        <v>928</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>856</v>
+        <v>1038</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-314</v>
+        <v>-110</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1432,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-311</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>542</v>
+        <v>943</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>856</v>
+        <v>1038</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-314</v>
+        <v>-95</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1477,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1056</v>
+        <v>951</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>856</v>
+        <v>1038</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>200</v>
+        <v>-87</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1508,7 +1517,7 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1522,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-411</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>474</v>
+        <v>1196</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>856</v>
+        <v>1038</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-382</v>
+        <v>158</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1567,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,17 +1586,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>566</v>
+        <v>1126</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-290</v>
+        <v>200</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46</v>
@@ -1598,9 +1607,9 @@
       <c r="I25" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1612,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1622,28 +1631,28 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-269</t>
+          <t>EgyptAir MS-8246</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>678</v>
+        <v>1196</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>856</v>
+        <v>1038</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-178</v>
+        <v>158</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1657,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1056</v>
+        <v>609</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>200</v>
+        <v>-115</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1688,7 +1697,7 @@
       <c r="I27" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1702,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1712,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>Saudia SV-321</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-248</v>
+        <v>-112</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1733,9 +1742,9 @@
       <c r="I28" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1747,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1757,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>698</v>
+        <v>649</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-158</v>
+        <v>-75</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46</v>
@@ -1778,7 +1787,7 @@
       <c r="I29" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1792,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1802,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>706</v>
+        <v>544</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-150</v>
+        <v>-180</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1823,9 +1832,9 @@
       <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1837,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1847,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-8246</t>
+          <t>Saudia SV-311</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1056</v>
+        <v>612</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>856</v>
+        <v>724</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>200</v>
+        <v>-112</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46</v>
@@ -1868,7 +1877,7 @@
       <c r="I31" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1882,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1892,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-690</t>
+          <t>EgyptAir MS-650</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>556</v>
+        <v>724</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>10</v>
+        <v>-183</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1913,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1927,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1937,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-650</t>
+          <t>EgyptAir MS-652</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>683</v>
+        <v>601</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>25</v>
+        <v>-123</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1958,7 +1967,7 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1972,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1982,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-652</t>
+          <t>EgyptAir MS-648</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-35</v>
+        <v>-115</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2003,7 +2012,7 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2017,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2027,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-648</t>
+          <t>EgyptAir MS-690</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>631</v>
+        <v>499</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>658</v>
+        <v>724</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-27</v>
+        <v>-225</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2048,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2062,43 +2071,718 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-650</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-138</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>706</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>724</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-313</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>03-AUG-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-417</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-121</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>06-AUG-26</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-464</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-652</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>586</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-648</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>594</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>658</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-64</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>06-AUG-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>EgyptAir MS-690</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n">
-        <v>641</v>
-      </c>
-      <c r="E36" s="2" t="n">
+      <c r="D42" s="2" t="n">
+        <v>604</v>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>658</v>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>-17</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="F42" s="2" t="n">
+        <v>-54</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>20-AUG-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-323</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-323</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>27-AUG-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-311</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>31-AUG-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-313</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>10-SEP-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-690</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>529</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>14-SEP-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-464</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-417</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>537</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>505</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
